--- a/df_raw.xlsx
+++ b/df_raw.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C3006911\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C3006911\Documents\Macro Research\2. SVAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE11AEC5-326D-4809-BF8D-7D89D66D895D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986B878B-664C-4E9F-B421-E1C186E48652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
